--- a/artfynd/A 35502-2024 artfynd.xlsx
+++ b/artfynd/A 35502-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132086804</v>
+        <v>132086863</v>
       </c>
       <c r="B2" t="n">
-        <v>83308</v>
+        <v>83343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6486</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599664</v>
+        <v>599652</v>
       </c>
       <c r="R2" t="n">
-        <v>7027663</v>
+        <v>7027640</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -769,6 +769,2127 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132086838</v>
+      </c>
+      <c r="B3" t="n">
+        <v>83353</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>310</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nordlig nållav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chaenotheca laevigata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Moforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>599679</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7027586</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Fingal Gyllang, Lars Salomon, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132086818</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92245</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>658</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Moforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>599640</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7027666</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Fingal Gyllang, Lars Salomon, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128195924</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92083</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Resele, Sorte, Resele s:n, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>599648</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7027672</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132086865</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2064</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kilporing</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Skeletocutis kuehneri</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>A.David</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Moforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>599647</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7027675</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Fingal Gyllang, Lars Salomon, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132086803</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83356</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6486</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skuggnål</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chaenotheca sphaerocephala</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Moforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>599632</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7027666</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Fingal Gyllang, Lars Salomon, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132086804</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83356</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6486</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skuggnål</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chaenotheca sphaerocephala</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Moforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>599664</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7027663</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Fingal Gyllang, Lars Salomon, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132086805</v>
+      </c>
+      <c r="B9" t="n">
+        <v>83356</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6486</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skuggnål</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenotheca sphaerocephala</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Moforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>599684</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7027575</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Fingal Gyllang, Lars Salomon, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132086806</v>
+      </c>
+      <c r="B10" t="n">
+        <v>83356</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6486</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skuggnål</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chaenotheca sphaerocephala</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Moforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>599682</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7027590</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Fingal Gyllang, Lars Salomon, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132086777</v>
+      </c>
+      <c r="B11" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Moforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>599641</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7027680</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Fingal Gyllang, Lars Salomon, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132086868</v>
+      </c>
+      <c r="B12" t="n">
+        <v>44182</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Moforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>599673</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7027601</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Fingal Gyllang, Lars Salomon, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132086766</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Moforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>599647</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7027677</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Fingal Gyllang, Stina Hällholm, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132086894</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Moforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>599678</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7027608</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Fingal Gyllang, Lars Salomon, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132086801</v>
+      </c>
+      <c r="B15" t="n">
+        <v>106141</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221101</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Springkorn</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Impatiens noli-tangere</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Moforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>599509</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7027909</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Fingal Gyllang, Lars Salomon, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132086887</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Moforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>599691</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7027576</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Fingal Gyllang, Lars Salomon, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132086888</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Moforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>599681</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7027562</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Fingal Gyllang, Lars Salomon, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132086783</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101305</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Moforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>599693</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7027574</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Fingal Gyllang, Lars Salomon, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132086829</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Moforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>599649</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7027673</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Fingal Gyllang, Lars Salomon, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132086834</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Moforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>599540</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7027835</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Fingal Gyllang, Lars Salomon, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132086842</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101293</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Moforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>599545</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7027835</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Fingal Gyllang, Lars Salomon, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128139373</v>
+      </c>
+      <c r="B22" t="n">
+        <v>89870</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>236437</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Brun klibbskivling</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Limacella glioderma</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Maire</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Resele, Sorte, Resele s:n, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>599648</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7027672</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132086885</v>
+      </c>
+      <c r="B23" t="n">
+        <v>89935</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>236437</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Brun klibbskivling</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Limacella glioderma</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Maire</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Moforsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>599633</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7027663</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Fingal Gyllang, Lars Salomon, Anders Haglund</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
         <is>
           <t>Naturvärdesinventering (NVI)</t>
         </is>

--- a/artfynd/A 35502-2024 artfynd.xlsx
+++ b/artfynd/A 35502-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086863</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086838</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086818</t>
         </is>
       </c>
     </row>
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128195924</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086865</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086803</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086804</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086805</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086806</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086777</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086868</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086766</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086894</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086801</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086887</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086888</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086783</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086829</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2591,6 +2686,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086834</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2690,6 +2790,11 @@
       <c r="AY21" t="inlineStr">
         <is>
           <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086842</t>
         </is>
       </c>
     </row>
@@ -2793,6 +2898,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128139373</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2894,8 +3004,37 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132086885</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>